--- a/artfynd/A 41576-2022 artfynd.xlsx
+++ b/artfynd/A 41576-2022 artfynd.xlsx
@@ -777,7 +777,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Zsombor Károlyi</t>
+          <t>Zsombor Károlyi, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Zsombor Károlyi</t>
+          <t>Zsombor Károlyi, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 41576-2022 artfynd.xlsx
+++ b/artfynd/A 41576-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130746041</v>
       </c>
       <c r="B2" t="n">
-        <v>58226</v>
+        <v>58234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Zsombor Károlyi, Ralf Lundmark</t>
+          <t>Ralf Lundmark, Zsombor Károlyi</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -787,7 +787,7 @@
         <v>130746037</v>
       </c>
       <c r="B3" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Zsombor Károlyi, Ralf Lundmark</t>
+          <t>Ralf Lundmark, Zsombor Károlyi</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 41576-2022 artfynd.xlsx
+++ b/artfynd/A 41576-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130746041</v>
       </c>
       <c r="B2" t="n">
-        <v>58234</v>
+        <v>58235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>130746037</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41576-2022 artfynd.xlsx
+++ b/artfynd/A 41576-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130746041</v>
       </c>
       <c r="B2" t="n">
-        <v>58235</v>
+        <v>58236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>130746037</v>
       </c>
       <c r="B3" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41576-2022 artfynd.xlsx
+++ b/artfynd/A 41576-2022 artfynd.xlsx
@@ -777,7 +777,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Zsombor Károlyi, Ralf Lundmark</t>
+          <t>Ralf Lundmark, Zsombor Károlyi</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Zsombor Károlyi, Ralf Lundmark</t>
+          <t>Ralf Lundmark, Zsombor Károlyi</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
